--- a/acs_pums_mappings.xlsx
+++ b/acs_pums_mappings.xlsx
@@ -1,24 +1,28 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10709"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10114"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/fblackin/Desktop/SUMMER2023/ResearchRotation/github_acres/synthpop-bookdown/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://bushare.sharepoint.com/sites/GRP-SPH-EH-ACRES/ACRES_Documents/AIM 2 - Data/Synthetic Population/RBookdown/synthpop-bookdown/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{35B595B6-11B4-164D-BACC-B3FB8343308B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="348" documentId="13_ncr:1_{35B595B6-11B4-164D-BACC-B3FB8343308B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{D1DE554A-F0DE-234D-A1DA-21E840E74F87}"/>
   <bookViews>
-    <workbookView xWindow="1680" yWindow="1400" windowWidth="27640" windowHeight="16940" xr2:uid="{9757DA40-1C4D-5840-8E2D-D605A76A9DB2}"/>
+    <workbookView xWindow="1080" yWindow="760" windowWidth="27640" windowHeight="16940" activeTab="3" xr2:uid="{9757DA40-1C4D-5840-8E2D-D605A76A9DB2}"/>
   </bookViews>
   <sheets>
-    <sheet name="B01001" sheetId="1" r:id="rId1"/>
-    <sheet name="B15001" sheetId="2" r:id="rId2"/>
-    <sheet name="B19037_age" sheetId="3" r:id="rId3"/>
-    <sheet name="B19037_income" sheetId="4" r:id="rId4"/>
-    <sheet name="B25007_age" sheetId="5" r:id="rId5"/>
-    <sheet name="B25007_tenure" sheetId="6" r:id="rId6"/>
+    <sheet name="B04006_ancestry" sheetId="9" r:id="rId1"/>
+    <sheet name="B03001_hispanic" sheetId="10" r:id="rId2"/>
+    <sheet name="B01001" sheetId="1" r:id="rId3"/>
+    <sheet name="DP04_rooms" sheetId="7" r:id="rId4"/>
+    <sheet name="DP04_yearbuilt" sheetId="8" r:id="rId5"/>
+    <sheet name="B15001" sheetId="2" r:id="rId6"/>
+    <sheet name="B19037_age" sheetId="3" r:id="rId7"/>
+    <sheet name="B19037_income" sheetId="4" r:id="rId8"/>
+    <sheet name="B25007_age" sheetId="5" r:id="rId9"/>
+    <sheet name="B25007_tenure" sheetId="6" r:id="rId10"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -41,7 +45,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="186" uniqueCount="119">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="624" uniqueCount="532">
   <si>
     <t>ACS Category</t>
   </si>
@@ -398,6 +402,1245 @@
   </si>
   <si>
     <t>Householder 45-64 years</t>
+  </si>
+  <si>
+    <t>1 Room</t>
+  </si>
+  <si>
+    <t>2 Rooms</t>
+  </si>
+  <si>
+    <t>3 Rooms</t>
+  </si>
+  <si>
+    <t>4 Rooms</t>
+  </si>
+  <si>
+    <t>5 Rooms</t>
+  </si>
+  <si>
+    <t>6 Rooms</t>
+  </si>
+  <si>
+    <t>7 Rooms</t>
+  </si>
+  <si>
+    <t>8 Rooms</t>
+  </si>
+  <si>
+    <t>9 or more rooms</t>
+  </si>
+  <si>
+    <t>…</t>
+  </si>
+  <si>
+    <t>Built.2020.or.later</t>
+  </si>
+  <si>
+    <t>Built.2010.to.2019</t>
+  </si>
+  <si>
+    <t>Built.2000.to.2009</t>
+  </si>
+  <si>
+    <t>Built.1990.to.1999</t>
+  </si>
+  <si>
+    <t>Built.1980.to.1989</t>
+  </si>
+  <si>
+    <t>Built.1970.to.1979</t>
+  </si>
+  <si>
+    <t>Built.1960.to.1969</t>
+  </si>
+  <si>
+    <t>Built.1950.to.1959</t>
+  </si>
+  <si>
+    <t>Built.1940.to.1949</t>
+  </si>
+  <si>
+    <t>Built.1939.or.earlier</t>
+  </si>
+  <si>
+    <t>Built.2020</t>
+  </si>
+  <si>
+    <t>Built.2021</t>
+  </si>
+  <si>
+    <t>Alsatian</t>
+  </si>
+  <si>
+    <t>Austrian</t>
+  </si>
+  <si>
+    <t>Basque</t>
+  </si>
+  <si>
+    <t>Belgian</t>
+  </si>
+  <si>
+    <t>Flemish</t>
+  </si>
+  <si>
+    <t>British</t>
+  </si>
+  <si>
+    <t>British Isles</t>
+  </si>
+  <si>
+    <t>Danish</t>
+  </si>
+  <si>
+    <t>Dutch</t>
+  </si>
+  <si>
+    <t>English</t>
+  </si>
+  <si>
+    <t>Finnish</t>
+  </si>
+  <si>
+    <t>French</t>
+  </si>
+  <si>
+    <t>German</t>
+  </si>
+  <si>
+    <t>Prussian</t>
+  </si>
+  <si>
+    <t>Greek</t>
+  </si>
+  <si>
+    <t>Icelander</t>
+  </si>
+  <si>
+    <t>Irish</t>
+  </si>
+  <si>
+    <t>Italian</t>
+  </si>
+  <si>
+    <t>Sicilian</t>
+  </si>
+  <si>
+    <t>Luxembourger</t>
+  </si>
+  <si>
+    <t>Maltese</t>
+  </si>
+  <si>
+    <t>Norwegian</t>
+  </si>
+  <si>
+    <t>Portuguese</t>
+  </si>
+  <si>
+    <t>Scotch Irish</t>
+  </si>
+  <si>
+    <t>Scottish</t>
+  </si>
+  <si>
+    <t>Swedish</t>
+  </si>
+  <si>
+    <t>Swiss</t>
+  </si>
+  <si>
+    <t>Irish Scotch</t>
+  </si>
+  <si>
+    <t>Welsh</t>
+  </si>
+  <si>
+    <t>Scandinavian</t>
+  </si>
+  <si>
+    <t>Celtic</t>
+  </si>
+  <si>
+    <t>Albanian</t>
+  </si>
+  <si>
+    <t>Belorussian</t>
+  </si>
+  <si>
+    <t>Bulgarian</t>
+  </si>
+  <si>
+    <t>Croatian</t>
+  </si>
+  <si>
+    <t>Czech</t>
+  </si>
+  <si>
+    <t>Bohemian</t>
+  </si>
+  <si>
+    <t>Czechoslovakian</t>
+  </si>
+  <si>
+    <t>Estonian</t>
+  </si>
+  <si>
+    <t>German Russian</t>
+  </si>
+  <si>
+    <t>Rom</t>
+  </si>
+  <si>
+    <t>Hungarian</t>
+  </si>
+  <si>
+    <t>Latvian</t>
+  </si>
+  <si>
+    <t>Lithuanian</t>
+  </si>
+  <si>
+    <t>Macedonian</t>
+  </si>
+  <si>
+    <t>Montenegrin</t>
+  </si>
+  <si>
+    <t>Polish</t>
+  </si>
+  <si>
+    <t>Romanian</t>
+  </si>
+  <si>
+    <t>Moldavian</t>
+  </si>
+  <si>
+    <t>Russian</t>
+  </si>
+  <si>
+    <t>Serbian</t>
+  </si>
+  <si>
+    <t>Slovak</t>
+  </si>
+  <si>
+    <t>Slovene</t>
+  </si>
+  <si>
+    <t>Turkestani</t>
+  </si>
+  <si>
+    <t>Uzbeg</t>
+  </si>
+  <si>
+    <t>Georgia CIS</t>
+  </si>
+  <si>
+    <t>Ukrainian</t>
+  </si>
+  <si>
+    <t>Yugoslavian</t>
+  </si>
+  <si>
+    <t>Bosnian and Herzegovinian</t>
+  </si>
+  <si>
+    <t>Slavic</t>
+  </si>
+  <si>
+    <t>Central European</t>
+  </si>
+  <si>
+    <t>Northern European</t>
+  </si>
+  <si>
+    <t>Southern European</t>
+  </si>
+  <si>
+    <t>Western European</t>
+  </si>
+  <si>
+    <t>Eastern European</t>
+  </si>
+  <si>
+    <t>Germanic</t>
+  </si>
+  <si>
+    <t>European</t>
+  </si>
+  <si>
+    <t>Spaniard</t>
+  </si>
+  <si>
+    <t>Mexican</t>
+  </si>
+  <si>
+    <t>Mexican American</t>
+  </si>
+  <si>
+    <t>Mexicano</t>
+  </si>
+  <si>
+    <t>Chicano</t>
+  </si>
+  <si>
+    <t>Mexican American Indian</t>
+  </si>
+  <si>
+    <t>Mexican State</t>
+  </si>
+  <si>
+    <t>Mexican Indian</t>
+  </si>
+  <si>
+    <t>Costa Rican</t>
+  </si>
+  <si>
+    <t>Guatemalan</t>
+  </si>
+  <si>
+    <t>Honduran</t>
+  </si>
+  <si>
+    <t>Nicaraguan</t>
+  </si>
+  <si>
+    <t>Panamanian</t>
+  </si>
+  <si>
+    <t>Salvadoran</t>
+  </si>
+  <si>
+    <t>Central American</t>
+  </si>
+  <si>
+    <t>Argentinean</t>
+  </si>
+  <si>
+    <t>Bolivian</t>
+  </si>
+  <si>
+    <t>Chilean</t>
+  </si>
+  <si>
+    <t>Colombian</t>
+  </si>
+  <si>
+    <t>Ecuadorian</t>
+  </si>
+  <si>
+    <t>Paraguayan</t>
+  </si>
+  <si>
+    <t>Peruvian</t>
+  </si>
+  <si>
+    <t>Uruguayan</t>
+  </si>
+  <si>
+    <t>Venezuelan</t>
+  </si>
+  <si>
+    <t>South American</t>
+  </si>
+  <si>
+    <t>Latin American</t>
+  </si>
+  <si>
+    <t>Latin</t>
+  </si>
+  <si>
+    <t>Latino</t>
+  </si>
+  <si>
+    <t>Puerto Rican</t>
+  </si>
+  <si>
+    <t>Cuban</t>
+  </si>
+  <si>
+    <t>Dominican</t>
+  </si>
+  <si>
+    <t>Hispanic</t>
+  </si>
+  <si>
+    <t>Spanish</t>
+  </si>
+  <si>
+    <t>Spanish American</t>
+  </si>
+  <si>
+    <t>Bahamian</t>
+  </si>
+  <si>
+    <t>Barbadian</t>
+  </si>
+  <si>
+    <t>Belizean</t>
+  </si>
+  <si>
+    <t>Jamaican</t>
+  </si>
+  <si>
+    <t>Dutch West Indian</t>
+  </si>
+  <si>
+    <t>Trinidadian Tobagonian</t>
+  </si>
+  <si>
+    <t>British West Indian</t>
+  </si>
+  <si>
+    <t>Antigua and Barbuda</t>
+  </si>
+  <si>
+    <t>Grenadian</t>
+  </si>
+  <si>
+    <t>Vincent-Grenadine Islander</t>
+  </si>
+  <si>
+    <t>St Lucia Islander</t>
+  </si>
+  <si>
+    <t>West Indian</t>
+  </si>
+  <si>
+    <t>Haitian</t>
+  </si>
+  <si>
+    <t>Other West Indian</t>
+  </si>
+  <si>
+    <t>Brazilian</t>
+  </si>
+  <si>
+    <t>Guyanese</t>
+  </si>
+  <si>
+    <t>Algerian</t>
+  </si>
+  <si>
+    <t>Egyptian</t>
+  </si>
+  <si>
+    <t>Libyan (2017 or later)</t>
+  </si>
+  <si>
+    <t>Moroccan</t>
+  </si>
+  <si>
+    <t>North African</t>
+  </si>
+  <si>
+    <t>Iranian</t>
+  </si>
+  <si>
+    <t>Iraqi</t>
+  </si>
+  <si>
+    <t>Israeli</t>
+  </si>
+  <si>
+    <t>Jordanian</t>
+  </si>
+  <si>
+    <t>Lebanese</t>
+  </si>
+  <si>
+    <t>Saudi Arabian</t>
+  </si>
+  <si>
+    <t>Syrian</t>
+  </si>
+  <si>
+    <t>Armenian</t>
+  </si>
+  <si>
+    <t>Turkish</t>
+  </si>
+  <si>
+    <t>Yemeni</t>
+  </si>
+  <si>
+    <t>Kurdish</t>
+  </si>
+  <si>
+    <t>Palestinian</t>
+  </si>
+  <si>
+    <t>Assyrian</t>
+  </si>
+  <si>
+    <t>Chaldean</t>
+  </si>
+  <si>
+    <t>Mideast</t>
+  </si>
+  <si>
+    <t>Arab</t>
+  </si>
+  <si>
+    <t>Arabic</t>
+  </si>
+  <si>
+    <t>Other Arab</t>
+  </si>
+  <si>
+    <t>Cameroonian</t>
+  </si>
+  <si>
+    <t>Cape Verdean</t>
+  </si>
+  <si>
+    <t>Congolese</t>
+  </si>
+  <si>
+    <t>Ethiopian</t>
+  </si>
+  <si>
+    <t>Eritrean</t>
+  </si>
+  <si>
+    <t>Gambian (2017 or later)</t>
+  </si>
+  <si>
+    <t>Ghanaian</t>
+  </si>
+  <si>
+    <t>Guinean (2017 or later)</t>
+  </si>
+  <si>
+    <t>Kenyan</t>
+  </si>
+  <si>
+    <t>Liberian</t>
+  </si>
+  <si>
+    <t>Nigerian</t>
+  </si>
+  <si>
+    <t>Senegalese</t>
+  </si>
+  <si>
+    <t>Sierra Leonean</t>
+  </si>
+  <si>
+    <t>Somali</t>
+  </si>
+  <si>
+    <t>South African</t>
+  </si>
+  <si>
+    <t>Sudanese</t>
+  </si>
+  <si>
+    <t>Togo (2017 or later)</t>
+  </si>
+  <si>
+    <t>Other Subsaharan African</t>
+  </si>
+  <si>
+    <t>Ugandan</t>
+  </si>
+  <si>
+    <t>Zimbabwean (2017 or later)</t>
+  </si>
+  <si>
+    <t>Western African</t>
+  </si>
+  <si>
+    <t>African</t>
+  </si>
+  <si>
+    <t>Afghan</t>
+  </si>
+  <si>
+    <t>Bangladeshi</t>
+  </si>
+  <si>
+    <t>Bhutanese</t>
+  </si>
+  <si>
+    <t>Nepali</t>
+  </si>
+  <si>
+    <t>Asian Indian</t>
+  </si>
+  <si>
+    <t>Bengali</t>
+  </si>
+  <si>
+    <t>East Indian</t>
+  </si>
+  <si>
+    <t>Punjabi</t>
+  </si>
+  <si>
+    <t>Pakistani</t>
+  </si>
+  <si>
+    <t>Sri Lankan</t>
+  </si>
+  <si>
+    <t>Burmese</t>
+  </si>
+  <si>
+    <t>Cambodian</t>
+  </si>
+  <si>
+    <t>Chinese</t>
+  </si>
+  <si>
+    <t>Cantonese</t>
+  </si>
+  <si>
+    <t>Mongolian</t>
+  </si>
+  <si>
+    <t>Tibetan</t>
+  </si>
+  <si>
+    <t>Hong Kong (2017 or later)</t>
+  </si>
+  <si>
+    <t>Filipino</t>
+  </si>
+  <si>
+    <t>Indonesian</t>
+  </si>
+  <si>
+    <t>Japanese</t>
+  </si>
+  <si>
+    <t>Okinawan</t>
+  </si>
+  <si>
+    <t>Korean</t>
+  </si>
+  <si>
+    <t>Laotian</t>
+  </si>
+  <si>
+    <t>Hmong</t>
+  </si>
+  <si>
+    <t>Malaysian</t>
+  </si>
+  <si>
+    <t>Thai</t>
+  </si>
+  <si>
+    <t>Taiwanese</t>
+  </si>
+  <si>
+    <t>Vietnamese</t>
+  </si>
+  <si>
+    <t>Eurasian (2016 or earlier)</t>
+  </si>
+  <si>
+    <t>Asian</t>
+  </si>
+  <si>
+    <t>Other Asian</t>
+  </si>
+  <si>
+    <t>Australian</t>
+  </si>
+  <si>
+    <t>New Zealander</t>
+  </si>
+  <si>
+    <t>Polynesian</t>
+  </si>
+  <si>
+    <t>Hawaiian</t>
+  </si>
+  <si>
+    <t>Samoan</t>
+  </si>
+  <si>
+    <t>Tongan</t>
+  </si>
+  <si>
+    <t>Micronesian</t>
+  </si>
+  <si>
+    <t>Guamanian</t>
+  </si>
+  <si>
+    <t>Chamorro</t>
+  </si>
+  <si>
+    <t>Marshallese</t>
+  </si>
+  <si>
+    <t>Fijian</t>
+  </si>
+  <si>
+    <t>Pacific Islander</t>
+  </si>
+  <si>
+    <t>Other Pacific</t>
+  </si>
+  <si>
+    <t>Afro American</t>
+  </si>
+  <si>
+    <t>Afro</t>
+  </si>
+  <si>
+    <t>African American</t>
+  </si>
+  <si>
+    <t>Black</t>
+  </si>
+  <si>
+    <t>Negro</t>
+  </si>
+  <si>
+    <t>Creole</t>
+  </si>
+  <si>
+    <t>Central American Indian</t>
+  </si>
+  <si>
+    <t>South American Indian</t>
+  </si>
+  <si>
+    <t>Native American</t>
+  </si>
+  <si>
+    <t>Indian</t>
+  </si>
+  <si>
+    <t>Cherokee</t>
+  </si>
+  <si>
+    <t>American Indian</t>
+  </si>
+  <si>
+    <t>Aleut (2016 or earlier)</t>
+  </si>
+  <si>
+    <t>Eskimo</t>
+  </si>
+  <si>
+    <t>White</t>
+  </si>
+  <si>
+    <t>Anglo</t>
+  </si>
+  <si>
+    <t>Appalachian</t>
+  </si>
+  <si>
+    <t>Pennsylvania German</t>
+  </si>
+  <si>
+    <t>Canadian</t>
+  </si>
+  <si>
+    <t>French Canadian</t>
+  </si>
+  <si>
+    <t>Cajun</t>
+  </si>
+  <si>
+    <t>American</t>
+  </si>
+  <si>
+    <t>United States</t>
+  </si>
+  <si>
+    <t>Texas</t>
+  </si>
+  <si>
+    <t>North American</t>
+  </si>
+  <si>
+    <t>Mixture</t>
+  </si>
+  <si>
+    <t>Uncodable entries</t>
+  </si>
+  <si>
+    <t>Other groups</t>
+  </si>
+  <si>
+    <t>Other responses</t>
+  </si>
+  <si>
+    <t>Not reported</t>
+  </si>
+  <si>
+    <t>ACS ANCESTRY</t>
+  </si>
+  <si>
+    <t>PUMA ANCESTRY</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Arab:!!Egyptian                                                  </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Arab:!!Iraqi                                                     </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Arab:!!Jordanian                                                 </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Arab:!!Lebanese                                                  </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Arab:!!Moroccan                                                  </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Arab:!!Palestinian                                               </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Arab:!!Syrian                                                    </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Arab:!!Arab                                                      </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Arab:!!Other Arab                                                </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Armenian                                                         </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Afghan                                                           </t>
+  </si>
+  <si>
+    <t xml:space="preserve">  Australian                                                       </t>
+  </si>
+  <si>
+    <t xml:space="preserve">  Austrian                                                         </t>
+  </si>
+  <si>
+    <t xml:space="preserve">  Basque                                                           </t>
+  </si>
+  <si>
+    <t xml:space="preserve">   Albanian                                                         </t>
+  </si>
+  <si>
+    <t xml:space="preserve">   Alsatian                                                         </t>
+  </si>
+  <si>
+    <t xml:space="preserve">   American                                                         </t>
+  </si>
+  <si>
+    <t xml:space="preserve">  Assyrian/Chaldean/Syriac                                         </t>
+  </si>
+  <si>
+    <t xml:space="preserve">  Belgian                                                          </t>
+  </si>
+  <si>
+    <t xml:space="preserve">  Brazilian                                                        </t>
+  </si>
+  <si>
+    <t xml:space="preserve">  British                                                          </t>
+  </si>
+  <si>
+    <t xml:space="preserve">  Bulgarian                                                        </t>
+  </si>
+  <si>
+    <t xml:space="preserve">  Cajun                                                            </t>
+  </si>
+  <si>
+    <t xml:space="preserve">  Canadian                                                         </t>
+  </si>
+  <si>
+    <t xml:space="preserve">  Carpatho Rusyn                                                   </t>
+  </si>
+  <si>
+    <t xml:space="preserve">  Celtic                                                           </t>
+  </si>
+  <si>
+    <t xml:space="preserve">  Croatian                                                         </t>
+  </si>
+  <si>
+    <t xml:space="preserve">  Cypriot                                                          </t>
+  </si>
+  <si>
+    <t xml:space="preserve">  Czech                                                            </t>
+  </si>
+  <si>
+    <t xml:space="preserve">  Czechoslovakian                                                  </t>
+  </si>
+  <si>
+    <t xml:space="preserve">  Danish                                                           </t>
+  </si>
+  <si>
+    <t xml:space="preserve">  Dutch                                                            </t>
+  </si>
+  <si>
+    <t xml:space="preserve">  Estonian                                                         </t>
+  </si>
+  <si>
+    <t xml:space="preserve">  European                                                         </t>
+  </si>
+  <si>
+    <t xml:space="preserve">  French (except Basque)                                           </t>
+  </si>
+  <si>
+    <t xml:space="preserve">  German                                                           </t>
+  </si>
+  <si>
+    <t xml:space="preserve">  German Russian                                                   </t>
+  </si>
+  <si>
+    <t xml:space="preserve">  Greek                                                            </t>
+  </si>
+  <si>
+    <t xml:space="preserve">  Guyanese                                                         </t>
+  </si>
+  <si>
+    <t xml:space="preserve">  Hungarian                                                        </t>
+  </si>
+  <si>
+    <t xml:space="preserve">  Icelander                                                        </t>
+  </si>
+  <si>
+    <t xml:space="preserve">  Iranian                                                          </t>
+  </si>
+  <si>
+    <t xml:space="preserve">  Irish                                                            </t>
+  </si>
+  <si>
+    <t xml:space="preserve">  Israeli                                                          </t>
+  </si>
+  <si>
+    <t xml:space="preserve">  Italian                                                          </t>
+  </si>
+  <si>
+    <t xml:space="preserve">  Latvian                                                          </t>
+  </si>
+  <si>
+    <t xml:space="preserve">  Lithuanian                                                       </t>
+  </si>
+  <si>
+    <t xml:space="preserve">  Luxembourger                                                     </t>
+  </si>
+  <si>
+    <t xml:space="preserve">  Macedonian                                                       </t>
+  </si>
+  <si>
+    <t xml:space="preserve">  Maltese                                                          </t>
+  </si>
+  <si>
+    <t xml:space="preserve">  New Zealander                                                    </t>
+  </si>
+  <si>
+    <t xml:space="preserve">  Northern European                                                </t>
+  </si>
+  <si>
+    <t xml:space="preserve">  Norwegian                                                        </t>
+  </si>
+  <si>
+    <t xml:space="preserve">  Pennsylvania German                                              </t>
+  </si>
+  <si>
+    <t xml:space="preserve">  Polish                                                           </t>
+  </si>
+  <si>
+    <t xml:space="preserve">  Portuguese                                                       </t>
+  </si>
+  <si>
+    <t xml:space="preserve">  Romanian                                                         </t>
+  </si>
+  <si>
+    <t xml:space="preserve">  Russian                                                          </t>
+  </si>
+  <si>
+    <t xml:space="preserve">  Scandinavian                                                     </t>
+  </si>
+  <si>
+    <t xml:space="preserve">  Scotch-Irish                                                     </t>
+  </si>
+  <si>
+    <t xml:space="preserve">  Scottish                                                         </t>
+  </si>
+  <si>
+    <t xml:space="preserve">  Serbian                                                          </t>
+  </si>
+  <si>
+    <t xml:space="preserve">  Slavic                                                           </t>
+  </si>
+  <si>
+    <t xml:space="preserve">  Slovak                                                           </t>
+  </si>
+  <si>
+    <t xml:space="preserve">  Slovene                                                          </t>
+  </si>
+  <si>
+    <t xml:space="preserve">  Soviet Union                                                     </t>
+  </si>
+  <si>
+    <t xml:space="preserve">  Subsaharan African:!!Cape Verdean                                </t>
+  </si>
+  <si>
+    <t xml:space="preserve">  Subsaharan African:!!Ethiopian                                   </t>
+  </si>
+  <si>
+    <t xml:space="preserve">  Subsaharan African:!!Ghanaian                                    </t>
+  </si>
+  <si>
+    <t xml:space="preserve">  Subsaharan African:!!Kenyan                                      </t>
+  </si>
+  <si>
+    <t xml:space="preserve">  Subsaharan African:!!Liberian                                    </t>
+  </si>
+  <si>
+    <t xml:space="preserve">  Subsaharan African:!!Nigerian                                    </t>
+  </si>
+  <si>
+    <t xml:space="preserve">  Subsaharan African:!!Senegalese                                  </t>
+  </si>
+  <si>
+    <t xml:space="preserve">  Subsaharan African:!!Sierra Leonean                              </t>
+  </si>
+  <si>
+    <t xml:space="preserve">  Subsaharan African:!!Somali                                      </t>
+  </si>
+  <si>
+    <t xml:space="preserve">  Subsaharan African:!!South African                               </t>
+  </si>
+  <si>
+    <t xml:space="preserve">  Subsaharan African:!!Sudanese                                    </t>
+  </si>
+  <si>
+    <t xml:space="preserve">  Subsaharan African:!!Ugandan                                     </t>
+  </si>
+  <si>
+    <t xml:space="preserve">  Subsaharan African:!!Zimbabwean                                  </t>
+  </si>
+  <si>
+    <t xml:space="preserve">  Subsaharan African:!!African                                     </t>
+  </si>
+  <si>
+    <t xml:space="preserve">  Subsaharan African:!!Other Subsaharan African                    </t>
+  </si>
+  <si>
+    <t xml:space="preserve">  Swedish                                                          </t>
+  </si>
+  <si>
+    <t xml:space="preserve">  Swiss                                                            </t>
+  </si>
+  <si>
+    <t xml:space="preserve">  Turkish                                                          </t>
+  </si>
+  <si>
+    <t xml:space="preserve">  Ukrainian                                                        </t>
+  </si>
+  <si>
+    <t xml:space="preserve">  Welsh                                                            </t>
+  </si>
+  <si>
+    <t xml:space="preserve">  West Indian (except Hispanic groups):!!Bahamian                  </t>
+  </si>
+  <si>
+    <t xml:space="preserve">  West Indian (except Hispanic groups):!!Barbadian                 </t>
+  </si>
+  <si>
+    <t xml:space="preserve">  West Indian (except Hispanic groups):!!Belizean                  </t>
+  </si>
+  <si>
+    <t xml:space="preserve">  West Indian (except Hispanic groups):!!Bermudan                  </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> West Indian (except Hispanic groups):!!British West Indian       </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> West Indian (except Hispanic groups):!!Dutch West Indian         </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> West Indian (except Hispanic groups):!!Haitian                   </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> West Indian (except Hispanic groups):!!Jamaican                  </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> West Indian (except Hispanic groups):!!Trinidadian and Tobagonian</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> West Indian (except Hispanic groups):!!U.S. Virgin Islander      </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> West Indian (except Hispanic groups):!!West Indian               </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> West Indian (except Hispanic groups):!!Other West Indian         </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Yugoslavian                                                      </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Other groups                                                     </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Unclassified or not reported </t>
+  </si>
+  <si>
+    <t>PUMS Hispanic</t>
+  </si>
+  <si>
+    <t>Not Spanish/Hispanic/Latino </t>
+  </si>
+  <si>
+    <t>Mexican </t>
+  </si>
+  <si>
+    <t>Puerto Rican </t>
+  </si>
+  <si>
+    <t>Cuban </t>
+  </si>
+  <si>
+    <t>Dominican </t>
+  </si>
+  <si>
+    <t>Costa Rican </t>
+  </si>
+  <si>
+    <t>Guatemalan </t>
+  </si>
+  <si>
+    <t>Honduran </t>
+  </si>
+  <si>
+    <t>Nicaraguan </t>
+  </si>
+  <si>
+    <t>Panamanian </t>
+  </si>
+  <si>
+    <t>Salvadoran </t>
+  </si>
+  <si>
+    <t>Other Central American </t>
+  </si>
+  <si>
+    <t>Argentinean </t>
+  </si>
+  <si>
+    <t>Bolivian </t>
+  </si>
+  <si>
+    <t>Chilean </t>
+  </si>
+  <si>
+    <t>Colombian </t>
+  </si>
+  <si>
+    <t>Ecuadorian </t>
+  </si>
+  <si>
+    <t>Paraguayan </t>
+  </si>
+  <si>
+    <t>Peruvian </t>
+  </si>
+  <si>
+    <t>Uruguayan </t>
+  </si>
+  <si>
+    <t>Venezuelan </t>
+  </si>
+  <si>
+    <t>Other South American </t>
+  </si>
+  <si>
+    <t>Spaniard </t>
+  </si>
+  <si>
+    <t>All Other Spanish/Hispanic/Latino </t>
+  </si>
+  <si>
+    <t>ACS Hispanic</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Not Hispanic or Latino        </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Mexican                       </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Puerto Rican                  </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Cuban                         </t>
+  </si>
+  <si>
+    <t>Dominican (Dominican Republic)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Costa Rican                   </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Guatemalan                    </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Honduran                      </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Nicaraguan                    </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Panamanian                    </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Salvadoran                    </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Other Central American        </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Argentinean                   </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Bolivian                      </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Chilean                       </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Colombian                     </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ecuadorian                    </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Paraguayan                    </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Peruvian                      </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Uruguayan                     </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Venezuelan                    </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Other South American          </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Spaniard                      </t>
+  </si>
+  <si>
+    <t xml:space="preserve">All other Hispanic or Latino  </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Spanish                       </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Spanish American              </t>
   </si>
 </sst>
 </file>
@@ -439,8 +1682,12 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -754,6 +2001,1844 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{85D24BE3-686D-1D4B-9563-73C4A873AD58}">
+  <dimension ref="A1:B242"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
+  <cols>
+    <col min="1" max="1" width="58" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="24.5" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A1" t="s">
+        <v>377</v>
+      </c>
+      <c r="B1" t="s">
+        <v>378</v>
+      </c>
+    </row>
+    <row r="2" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A2" t="s">
+        <v>393</v>
+      </c>
+      <c r="B2" t="s">
+        <v>172</v>
+      </c>
+    </row>
+    <row r="3" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A3" t="s">
+        <v>394</v>
+      </c>
+      <c r="B3" t="s">
+        <v>141</v>
+      </c>
+    </row>
+    <row r="4" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A4" t="s">
+        <v>395</v>
+      </c>
+      <c r="B4" t="s">
+        <v>368</v>
+      </c>
+    </row>
+    <row r="5" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A5" t="s">
+        <v>396</v>
+      </c>
+      <c r="B5" t="s">
+        <v>275</v>
+      </c>
+    </row>
+    <row r="6" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A6" t="s">
+        <v>396</v>
+      </c>
+      <c r="B6" t="s">
+        <v>276</v>
+      </c>
+    </row>
+    <row r="7" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A7" t="s">
+        <v>390</v>
+      </c>
+      <c r="B7" t="s">
+        <v>334</v>
+      </c>
+    </row>
+    <row r="8" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A8" t="s">
+        <v>391</v>
+      </c>
+      <c r="B8" t="s">
+        <v>142</v>
+      </c>
+    </row>
+    <row r="9" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A9" t="s">
+        <v>392</v>
+      </c>
+      <c r="B9" t="s">
+        <v>143</v>
+      </c>
+    </row>
+    <row r="10" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A10" t="s">
+        <v>397</v>
+      </c>
+      <c r="B10" t="s">
+        <v>144</v>
+      </c>
+    </row>
+    <row r="11" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A11" t="s">
+        <v>398</v>
+      </c>
+      <c r="B11" t="s">
+        <v>256</v>
+      </c>
+    </row>
+    <row r="12" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A12" t="s">
+        <v>399</v>
+      </c>
+      <c r="B12" t="s">
+        <v>146</v>
+      </c>
+    </row>
+    <row r="13" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A13" t="s">
+        <v>400</v>
+      </c>
+      <c r="B13" t="s">
+        <v>174</v>
+      </c>
+    </row>
+    <row r="14" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A14" t="s">
+        <v>401</v>
+      </c>
+      <c r="B14" t="s">
+        <v>367</v>
+      </c>
+    </row>
+    <row r="15" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A15" t="s">
+        <v>402</v>
+      </c>
+      <c r="B15" t="s">
+        <v>365</v>
+      </c>
+    </row>
+    <row r="16" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A16" t="s">
+        <v>403</v>
+      </c>
+    </row>
+    <row r="17" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A17" t="s">
+        <v>404</v>
+      </c>
+      <c r="B17" t="s">
+        <v>171</v>
+      </c>
+    </row>
+    <row r="18" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A18" t="s">
+        <v>405</v>
+      </c>
+      <c r="B18" t="s">
+        <v>175</v>
+      </c>
+    </row>
+    <row r="19" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A19" t="s">
+        <v>406</v>
+      </c>
+    </row>
+    <row r="20" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A20" t="s">
+        <v>407</v>
+      </c>
+      <c r="B20" t="s">
+        <v>176</v>
+      </c>
+    </row>
+    <row r="21" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A21" t="s">
+        <v>408</v>
+      </c>
+      <c r="B21" t="s">
+        <v>178</v>
+      </c>
+    </row>
+    <row r="22" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A22" t="s">
+        <v>409</v>
+      </c>
+      <c r="B22" t="s">
+        <v>148</v>
+      </c>
+    </row>
+    <row r="23" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A23" t="s">
+        <v>410</v>
+      </c>
+      <c r="B23" t="s">
+        <v>149</v>
+      </c>
+    </row>
+    <row r="24" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A24" t="s">
+        <v>411</v>
+      </c>
+      <c r="B24" t="s">
+        <v>179</v>
+      </c>
+    </row>
+    <row r="25" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A25" t="s">
+        <v>412</v>
+      </c>
+      <c r="B25" t="s">
+        <v>207</v>
+      </c>
+    </row>
+    <row r="26" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A26" t="s">
+        <v>413</v>
+      </c>
+      <c r="B26" t="s">
+        <v>152</v>
+      </c>
+    </row>
+    <row r="27" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A27" t="s">
+        <v>414</v>
+      </c>
+      <c r="B27" t="s">
+        <v>153</v>
+      </c>
+    </row>
+    <row r="28" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A28" t="s">
+        <v>415</v>
+      </c>
+      <c r="B28" t="s">
+        <v>180</v>
+      </c>
+    </row>
+    <row r="29" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A29" t="s">
+        <v>416</v>
+      </c>
+      <c r="B29" t="s">
+        <v>155</v>
+      </c>
+    </row>
+    <row r="30" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A30" t="s">
+        <v>417</v>
+      </c>
+      <c r="B30" t="s">
+        <v>257</v>
+      </c>
+    </row>
+    <row r="31" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A31" t="s">
+        <v>418</v>
+      </c>
+      <c r="B31" t="s">
+        <v>182</v>
+      </c>
+    </row>
+    <row r="32" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A32" t="s">
+        <v>419</v>
+      </c>
+      <c r="B32" t="s">
+        <v>156</v>
+      </c>
+    </row>
+    <row r="33" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A33" t="s">
+        <v>420</v>
+      </c>
+      <c r="B33" t="s">
+        <v>263</v>
+      </c>
+    </row>
+    <row r="34" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A34" t="s">
+        <v>421</v>
+      </c>
+      <c r="B34" t="s">
+        <v>157</v>
+      </c>
+    </row>
+    <row r="35" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A35" t="s">
+        <v>422</v>
+      </c>
+      <c r="B35" t="s">
+        <v>265</v>
+      </c>
+    </row>
+    <row r="36" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A36" t="s">
+        <v>423</v>
+      </c>
+      <c r="B36" t="s">
+        <v>158</v>
+      </c>
+    </row>
+    <row r="37" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A37" t="s">
+        <v>424</v>
+      </c>
+      <c r="B37" t="s">
+        <v>183</v>
+      </c>
+    </row>
+    <row r="38" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A38" t="s">
+        <v>425</v>
+      </c>
+      <c r="B38" t="s">
+        <v>184</v>
+      </c>
+    </row>
+    <row r="39" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A39" t="s">
+        <v>426</v>
+      </c>
+      <c r="B39" t="s">
+        <v>160</v>
+      </c>
+    </row>
+    <row r="40" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A40" t="s">
+        <v>427</v>
+      </c>
+      <c r="B40" t="s">
+        <v>185</v>
+      </c>
+    </row>
+    <row r="41" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A41" t="s">
+        <v>428</v>
+      </c>
+      <c r="B41" t="s">
+        <v>161</v>
+      </c>
+    </row>
+    <row r="42" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A42" t="s">
+        <v>429</v>
+      </c>
+      <c r="B42" t="s">
+        <v>335</v>
+      </c>
+    </row>
+    <row r="43" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A43" t="s">
+        <v>430</v>
+      </c>
+      <c r="B43" t="s">
+        <v>202</v>
+      </c>
+    </row>
+    <row r="44" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A44" t="s">
+        <v>431</v>
+      </c>
+      <c r="B44" t="s">
+        <v>162</v>
+      </c>
+    </row>
+    <row r="45" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A45" t="s">
+        <v>432</v>
+      </c>
+      <c r="B45" t="s">
+        <v>364</v>
+      </c>
+    </row>
+    <row r="46" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A46" t="s">
+        <v>433</v>
+      </c>
+      <c r="B46" t="s">
+        <v>187</v>
+      </c>
+    </row>
+    <row r="47" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A47" t="s">
+        <v>434</v>
+      </c>
+      <c r="B47" t="s">
+        <v>163</v>
+      </c>
+    </row>
+    <row r="48" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A48" t="s">
+        <v>435</v>
+      </c>
+      <c r="B48" t="s">
+        <v>188</v>
+      </c>
+    </row>
+    <row r="49" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A49" t="s">
+        <v>436</v>
+      </c>
+      <c r="B49" t="s">
+        <v>190</v>
+      </c>
+    </row>
+    <row r="50" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A50" t="s">
+        <v>437</v>
+      </c>
+      <c r="B50" t="s">
+        <v>170</v>
+      </c>
+    </row>
+    <row r="51" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A51" t="s">
+        <v>438</v>
+      </c>
+      <c r="B51" t="s">
+        <v>164</v>
+      </c>
+    </row>
+    <row r="52" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A52" t="s">
+        <v>439</v>
+      </c>
+      <c r="B52" t="s">
+        <v>165</v>
+      </c>
+    </row>
+    <row r="53" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A53" t="s">
+        <v>440</v>
+      </c>
+      <c r="B53" t="s">
+        <v>191</v>
+      </c>
+    </row>
+    <row r="54" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A54" t="s">
+        <v>441</v>
+      </c>
+      <c r="B54" t="s">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="55" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A55" t="s">
+        <v>442</v>
+      </c>
+      <c r="B55" t="s">
+        <v>192</v>
+      </c>
+    </row>
+    <row r="56" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A56" t="s">
+        <v>443</v>
+      </c>
+      <c r="B56" t="s">
+        <v>193</v>
+      </c>
+    </row>
+    <row r="57" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A57" s="2" t="s">
+        <v>444</v>
+      </c>
+    </row>
+    <row r="58" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A58" t="s">
+        <v>458</v>
+      </c>
+      <c r="B58" t="s">
+        <v>302</v>
+      </c>
+    </row>
+    <row r="59" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A59" t="s">
+        <v>445</v>
+      </c>
+      <c r="B59" t="s">
+        <v>282</v>
+      </c>
+    </row>
+    <row r="60" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A60" t="s">
+        <v>446</v>
+      </c>
+      <c r="B60" t="s">
+        <v>284</v>
+      </c>
+    </row>
+    <row r="61" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A61" t="s">
+        <v>447</v>
+      </c>
+      <c r="B61" t="s">
+        <v>287</v>
+      </c>
+    </row>
+    <row r="62" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A62" t="s">
+        <v>448</v>
+      </c>
+      <c r="B62" t="s">
+        <v>289</v>
+      </c>
+    </row>
+    <row r="63" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A63" t="s">
+        <v>449</v>
+      </c>
+      <c r="B63" t="s">
+        <v>290</v>
+      </c>
+    </row>
+    <row r="64" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A64" t="s">
+        <v>450</v>
+      </c>
+      <c r="B64" t="s">
+        <v>291</v>
+      </c>
+    </row>
+    <row r="65" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A65" t="s">
+        <v>459</v>
+      </c>
+      <c r="B65" t="s">
+        <v>298</v>
+      </c>
+    </row>
+    <row r="66" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A66" t="s">
+        <v>451</v>
+      </c>
+      <c r="B66" t="s">
+        <v>292</v>
+      </c>
+    </row>
+    <row r="67" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A67" t="s">
+        <v>452</v>
+      </c>
+      <c r="B67" t="s">
+        <v>293</v>
+      </c>
+    </row>
+    <row r="68" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A68" t="s">
+        <v>453</v>
+      </c>
+      <c r="B68" t="s">
+        <v>294</v>
+      </c>
+    </row>
+    <row r="69" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A69" t="s">
+        <v>454</v>
+      </c>
+      <c r="B69" t="s">
+        <v>295</v>
+      </c>
+    </row>
+    <row r="70" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A70" t="s">
+        <v>455</v>
+      </c>
+      <c r="B70" t="s">
+        <v>296</v>
+      </c>
+    </row>
+    <row r="71" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A71" t="s">
+        <v>456</v>
+      </c>
+      <c r="B71" t="s">
+        <v>299</v>
+      </c>
+    </row>
+    <row r="72" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A72" t="s">
+        <v>457</v>
+      </c>
+      <c r="B72" t="s">
+        <v>195</v>
+      </c>
+    </row>
+    <row r="73" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A73" t="s">
+        <v>460</v>
+      </c>
+      <c r="B73" t="s">
+        <v>166</v>
+      </c>
+    </row>
+    <row r="74" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A74" t="s">
+        <v>461</v>
+      </c>
+      <c r="B74" t="s">
+        <v>167</v>
+      </c>
+    </row>
+    <row r="75" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A75" t="s">
+        <v>462</v>
+      </c>
+      <c r="B75" t="s">
+        <v>271</v>
+      </c>
+    </row>
+    <row r="76" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A76" t="s">
+        <v>463</v>
+      </c>
+      <c r="B76" t="s">
+        <v>197</v>
+      </c>
+    </row>
+    <row r="77" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A77" t="s">
+        <v>464</v>
+      </c>
+      <c r="B77" t="s">
+        <v>169</v>
+      </c>
+    </row>
+    <row r="78" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A78" t="s">
+        <v>465</v>
+      </c>
+      <c r="B78" t="s">
+        <v>242</v>
+      </c>
+    </row>
+    <row r="79" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A79" t="s">
+        <v>466</v>
+      </c>
+      <c r="B79" t="s">
+        <v>243</v>
+      </c>
+    </row>
+    <row r="80" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A80" t="s">
+        <v>467</v>
+      </c>
+      <c r="B80" t="s">
+        <v>244</v>
+      </c>
+    </row>
+    <row r="81" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A81" t="s">
+        <v>468</v>
+      </c>
+    </row>
+    <row r="82" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A82" t="s">
+        <v>478</v>
+      </c>
+      <c r="B82" t="s">
+        <v>374</v>
+      </c>
+    </row>
+    <row r="83" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A83" t="s">
+        <v>479</v>
+      </c>
+      <c r="B83" t="s">
+        <v>376</v>
+      </c>
+    </row>
+    <row r="84" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A84" t="s">
+        <v>469</v>
+      </c>
+      <c r="B84" t="s">
+        <v>248</v>
+      </c>
+    </row>
+    <row r="85" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A85" t="s">
+        <v>470</v>
+      </c>
+      <c r="B85" t="s">
+        <v>246</v>
+      </c>
+    </row>
+    <row r="86" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A86" t="s">
+        <v>471</v>
+      </c>
+      <c r="B86" t="s">
+        <v>254</v>
+      </c>
+    </row>
+    <row r="87" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A87" t="s">
+        <v>472</v>
+      </c>
+      <c r="B87" t="s">
+        <v>245</v>
+      </c>
+    </row>
+    <row r="88" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A88" t="s">
+        <v>476</v>
+      </c>
+      <c r="B88" t="s">
+        <v>255</v>
+      </c>
+    </row>
+    <row r="89" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A89" t="s">
+        <v>473</v>
+      </c>
+      <c r="B89" t="s">
+        <v>247</v>
+      </c>
+    </row>
+    <row r="90" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A90" t="s">
+        <v>474</v>
+      </c>
+    </row>
+    <row r="91" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A91" t="s">
+        <v>475</v>
+      </c>
+      <c r="B91" t="s">
+        <v>253</v>
+      </c>
+    </row>
+    <row r="92" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A92" t="s">
+        <v>477</v>
+      </c>
+      <c r="B92" t="s">
+        <v>198</v>
+      </c>
+    </row>
+    <row r="93" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A93" t="s">
+        <v>389</v>
+      </c>
+      <c r="B93" t="s">
+        <v>303</v>
+      </c>
+    </row>
+    <row r="94" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A94" t="s">
+        <v>386</v>
+      </c>
+      <c r="B94" t="s">
+        <v>278</v>
+      </c>
+    </row>
+    <row r="95" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A95" t="s">
+        <v>379</v>
+      </c>
+      <c r="B95" t="s">
+        <v>259</v>
+      </c>
+    </row>
+    <row r="96" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A96" t="s">
+        <v>380</v>
+      </c>
+      <c r="B96" t="s">
+        <v>264</v>
+      </c>
+    </row>
+    <row r="97" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A97" t="s">
+        <v>381</v>
+      </c>
+      <c r="B97" t="s">
+        <v>266</v>
+      </c>
+    </row>
+    <row r="98" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A98" t="s">
+        <v>382</v>
+      </c>
+      <c r="B98" t="s">
+        <v>267</v>
+      </c>
+    </row>
+    <row r="99" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A99" t="s">
+        <v>383</v>
+      </c>
+      <c r="B99" t="s">
+        <v>261</v>
+      </c>
+    </row>
+    <row r="100" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A100" t="s">
+        <v>387</v>
+      </c>
+      <c r="B100" t="s">
+        <v>280</v>
+      </c>
+    </row>
+    <row r="101" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A101" t="s">
+        <v>384</v>
+      </c>
+      <c r="B101" t="s">
+        <v>274</v>
+      </c>
+    </row>
+    <row r="102" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A102" t="s">
+        <v>385</v>
+      </c>
+      <c r="B102" t="s">
+        <v>269</v>
+      </c>
+    </row>
+    <row r="103" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A103" t="s">
+        <v>388</v>
+      </c>
+      <c r="B103" t="s">
+        <v>270</v>
+      </c>
+    </row>
+    <row r="104" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A104" t="s">
+        <v>205</v>
+      </c>
+      <c r="B104" t="s">
+        <v>205</v>
+      </c>
+    </row>
+    <row r="105" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A105" t="s">
+        <v>150</v>
+      </c>
+      <c r="B105" t="s">
+        <v>150</v>
+      </c>
+    </row>
+    <row r="106" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A106" t="s">
+        <v>151</v>
+      </c>
+      <c r="B106" t="s">
+        <v>151</v>
+      </c>
+    </row>
+    <row r="107" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A107" t="s">
+        <v>366</v>
+      </c>
+      <c r="B107" t="s">
+        <v>366</v>
+      </c>
+    </row>
+    <row r="108" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="B108" t="s">
+        <v>349</v>
+      </c>
+    </row>
+    <row r="109" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="B109" t="s">
+        <v>348</v>
+      </c>
+    </row>
+    <row r="110" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="B110" t="s">
+        <v>347</v>
+      </c>
+    </row>
+    <row r="111" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="B111" t="s">
+        <v>359</v>
+      </c>
+    </row>
+    <row r="112" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="B112" t="s">
+        <v>258</v>
+      </c>
+    </row>
+    <row r="113" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B113" t="s">
+        <v>358</v>
+      </c>
+    </row>
+    <row r="114" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B114" t="s">
+        <v>362</v>
+      </c>
+    </row>
+    <row r="115" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B115" t="s">
+        <v>249</v>
+      </c>
+    </row>
+    <row r="116" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B116" t="s">
+        <v>363</v>
+      </c>
+    </row>
+    <row r="117" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B117" t="s">
+        <v>279</v>
+      </c>
+    </row>
+    <row r="118" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B118" t="s">
+        <v>223</v>
+      </c>
+    </row>
+    <row r="119" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B119" t="s">
+        <v>332</v>
+      </c>
+    </row>
+    <row r="120" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B120" t="s">
+        <v>307</v>
+      </c>
+    </row>
+    <row r="121" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B121" t="s">
+        <v>304</v>
+      </c>
+    </row>
+    <row r="122" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B122" t="s">
+        <v>173</v>
+      </c>
+    </row>
+    <row r="123" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B123" t="s">
+        <v>308</v>
+      </c>
+    </row>
+    <row r="124" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B124" t="s">
+        <v>305</v>
+      </c>
+    </row>
+    <row r="125" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B125" t="s">
+        <v>350</v>
+      </c>
+    </row>
+    <row r="126" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B126" t="s">
+        <v>177</v>
+      </c>
+    </row>
+    <row r="127" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B127" t="s">
+        <v>224</v>
+      </c>
+    </row>
+    <row r="128" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B128" t="s">
+        <v>199</v>
+      </c>
+    </row>
+    <row r="129" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B129" t="s">
+        <v>147</v>
+      </c>
+    </row>
+    <row r="130" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B130" t="s">
+        <v>313</v>
+      </c>
+    </row>
+    <row r="131" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B131" t="s">
+        <v>314</v>
+      </c>
+    </row>
+    <row r="132" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B132" t="s">
+        <v>281</v>
+      </c>
+    </row>
+    <row r="133" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B133" t="s">
+        <v>316</v>
+      </c>
+    </row>
+    <row r="134" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B134" t="s">
+        <v>222</v>
+      </c>
+    </row>
+    <row r="135" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B135" t="s">
+        <v>353</v>
+      </c>
+    </row>
+    <row r="136" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B136" t="s">
+        <v>201</v>
+      </c>
+    </row>
+    <row r="137" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B137" t="s">
+        <v>342</v>
+      </c>
+    </row>
+    <row r="138" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B138" t="s">
+        <v>357</v>
+      </c>
+    </row>
+    <row r="139" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B139" t="s">
+        <v>212</v>
+      </c>
+    </row>
+    <row r="140" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B140" t="s">
+        <v>225</v>
+      </c>
+    </row>
+    <row r="141" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B141" t="s">
+        <v>315</v>
+      </c>
+    </row>
+    <row r="142" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B142" t="s">
+        <v>226</v>
+      </c>
+    </row>
+    <row r="143" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B143" t="s">
+        <v>283</v>
+      </c>
+    </row>
+    <row r="144" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B144" t="s">
+        <v>216</v>
+      </c>
+    </row>
+    <row r="145" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B145" t="s">
+        <v>352</v>
+      </c>
+    </row>
+    <row r="146" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B146" t="s">
+        <v>237</v>
+      </c>
+    </row>
+    <row r="147" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B147" t="s">
+        <v>238</v>
+      </c>
+    </row>
+    <row r="148" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B148" t="s">
+        <v>309</v>
+      </c>
+    </row>
+    <row r="149" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B149" t="s">
+        <v>227</v>
+      </c>
+    </row>
+    <row r="150" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B150" t="s">
+        <v>285</v>
+      </c>
+    </row>
+    <row r="151" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B151" t="s">
+        <v>360</v>
+      </c>
+    </row>
+    <row r="152" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B152" t="s">
+        <v>331</v>
+      </c>
+    </row>
+    <row r="153" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B153" t="s">
+        <v>344</v>
+      </c>
+    </row>
+    <row r="154" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B154" t="s">
+        <v>320</v>
+      </c>
+    </row>
+    <row r="155" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B155" t="s">
+        <v>145</v>
+      </c>
+    </row>
+    <row r="156" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B156" t="s">
+        <v>286</v>
+      </c>
+    </row>
+    <row r="157" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B157" t="s">
+        <v>196</v>
+      </c>
+    </row>
+    <row r="158" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B158" t="s">
+        <v>206</v>
+      </c>
+    </row>
+    <row r="159" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B159" t="s">
+        <v>250</v>
+      </c>
+    </row>
+    <row r="160" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B160" t="s">
+        <v>341</v>
+      </c>
+    </row>
+    <row r="161" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B161" t="s">
+        <v>217</v>
+      </c>
+    </row>
+    <row r="162" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B162" t="s">
+        <v>288</v>
+      </c>
+    </row>
+    <row r="163" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B163" t="s">
+        <v>337</v>
+      </c>
+    </row>
+    <row r="164" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B164" t="s">
+        <v>239</v>
+      </c>
+    </row>
+    <row r="165" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B165" t="s">
+        <v>326</v>
+      </c>
+    </row>
+    <row r="166" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B166" t="s">
+        <v>218</v>
+      </c>
+    </row>
+    <row r="167" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B167" t="s">
+        <v>319</v>
+      </c>
+    </row>
+    <row r="168" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B168" t="s">
+        <v>356</v>
+      </c>
+    </row>
+    <row r="169" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B169" t="s">
+        <v>321</v>
+      </c>
+    </row>
+    <row r="170" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B170" t="s">
+        <v>168</v>
+      </c>
+    </row>
+    <row r="171" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B171" t="s">
+        <v>322</v>
+      </c>
+    </row>
+    <row r="172" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B172" t="s">
+        <v>324</v>
+      </c>
+    </row>
+    <row r="173" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B173" t="s">
+        <v>273</v>
+      </c>
+    </row>
+    <row r="174" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B174" t="s">
+        <v>325</v>
+      </c>
+    </row>
+    <row r="175" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B175" t="s">
+        <v>234</v>
+      </c>
+    </row>
+    <row r="176" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B176" t="s">
+        <v>233</v>
+      </c>
+    </row>
+    <row r="177" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B177" t="s">
+        <v>235</v>
+      </c>
+    </row>
+    <row r="178" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B178" t="s">
+        <v>260</v>
+      </c>
+    </row>
+    <row r="179" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B179" t="s">
+        <v>327</v>
+      </c>
+    </row>
+    <row r="180" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B180" t="s">
+        <v>343</v>
+      </c>
+    </row>
+    <row r="181" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B181" t="s">
+        <v>209</v>
+      </c>
+    </row>
+    <row r="182" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B182" t="s">
+        <v>210</v>
+      </c>
+    </row>
+    <row r="183" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B183" t="s">
+        <v>213</v>
+      </c>
+    </row>
+    <row r="184" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B184" t="s">
+        <v>215</v>
+      </c>
+    </row>
+    <row r="185" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B185" t="s">
+        <v>214</v>
+      </c>
+    </row>
+    <row r="186" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B186" t="s">
+        <v>211</v>
+      </c>
+    </row>
+    <row r="187" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B187" t="s">
+        <v>340</v>
+      </c>
+    </row>
+    <row r="188" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B188" t="s">
+        <v>277</v>
+      </c>
+    </row>
+    <row r="189" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B189" t="s">
+        <v>372</v>
+      </c>
+    </row>
+    <row r="190" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B190" t="s">
+        <v>189</v>
+      </c>
+    </row>
+    <row r="191" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B191" t="s">
+        <v>317</v>
+      </c>
+    </row>
+    <row r="192" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B192" t="s">
+        <v>186</v>
+      </c>
+    </row>
+    <row r="193" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B193" t="s">
+        <v>355</v>
+      </c>
+    </row>
+    <row r="194" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B194" t="s">
+        <v>351</v>
+      </c>
+    </row>
+    <row r="195" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B195" t="s">
+        <v>306</v>
+      </c>
+    </row>
+    <row r="196" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B196" t="s">
+        <v>219</v>
+      </c>
+    </row>
+    <row r="197" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B197" t="s">
+        <v>262</v>
+      </c>
+    </row>
+    <row r="198" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B198" t="s">
+        <v>371</v>
+      </c>
+    </row>
+    <row r="199" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B199" t="s">
+        <v>323</v>
+      </c>
+    </row>
+    <row r="200" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B200" t="s">
+        <v>333</v>
+      </c>
+    </row>
+    <row r="201" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B201" t="s">
+        <v>346</v>
+      </c>
+    </row>
+    <row r="202" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B202" t="s">
+        <v>375</v>
+      </c>
+    </row>
+    <row r="203" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B203" t="s">
+        <v>345</v>
+      </c>
+    </row>
+    <row r="204" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B204" t="s">
+        <v>311</v>
+      </c>
+    </row>
+    <row r="205" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B205" t="s">
+        <v>220</v>
+      </c>
+    </row>
+    <row r="206" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B206" t="s">
+        <v>228</v>
+      </c>
+    </row>
+    <row r="207" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B207" t="s">
+        <v>229</v>
+      </c>
+    </row>
+    <row r="208" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B208" t="s">
+        <v>336</v>
+      </c>
+    </row>
+    <row r="209" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B209" t="s">
+        <v>154</v>
+      </c>
+    </row>
+    <row r="210" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B210" t="s">
+        <v>236</v>
+      </c>
+    </row>
+    <row r="211" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B211" t="s">
+        <v>310</v>
+      </c>
+    </row>
+    <row r="212" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B212" t="s">
+        <v>181</v>
+      </c>
+    </row>
+    <row r="213" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B213" t="s">
+        <v>221</v>
+      </c>
+    </row>
+    <row r="214" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B214" t="s">
+        <v>338</v>
+      </c>
+    </row>
+    <row r="215" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B215" t="s">
+        <v>268</v>
+      </c>
+    </row>
+    <row r="216" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B216" t="s">
+        <v>159</v>
+      </c>
+    </row>
+    <row r="217" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B217" t="s">
+        <v>232</v>
+      </c>
+    </row>
+    <row r="218" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B218" t="s">
+        <v>354</v>
+      </c>
+    </row>
+    <row r="219" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B219" t="s">
+        <v>203</v>
+      </c>
+    </row>
+    <row r="220" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B220" t="s">
+        <v>208</v>
+      </c>
+    </row>
+    <row r="221" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B221" t="s">
+        <v>240</v>
+      </c>
+    </row>
+    <row r="222" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B222" t="s">
+        <v>241</v>
+      </c>
+    </row>
+    <row r="223" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B223" t="s">
+        <v>312</v>
+      </c>
+    </row>
+    <row r="224" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B224" t="s">
+        <v>252</v>
+      </c>
+    </row>
+    <row r="225" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B225" t="s">
+        <v>329</v>
+      </c>
+    </row>
+    <row r="226" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B226" t="s">
+        <v>328</v>
+      </c>
+    </row>
+    <row r="227" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B227" t="s">
+        <v>318</v>
+      </c>
+    </row>
+    <row r="228" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B228" t="s">
+        <v>297</v>
+      </c>
+    </row>
+    <row r="229" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B229" t="s">
+        <v>339</v>
+      </c>
+    </row>
+    <row r="230" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B230" t="s">
+        <v>194</v>
+      </c>
+    </row>
+    <row r="231" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B231" t="s">
+        <v>373</v>
+      </c>
+    </row>
+    <row r="232" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B232" t="s">
+        <v>369</v>
+      </c>
+    </row>
+    <row r="233" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B233" t="s">
+        <v>230</v>
+      </c>
+    </row>
+    <row r="234" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B234" t="s">
+        <v>231</v>
+      </c>
+    </row>
+    <row r="235" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B235" t="s">
+        <v>330</v>
+      </c>
+    </row>
+    <row r="236" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B236" t="s">
+        <v>251</v>
+      </c>
+    </row>
+    <row r="237" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B237" t="s">
+        <v>301</v>
+      </c>
+    </row>
+    <row r="238" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B238" t="s">
+        <v>204</v>
+      </c>
+    </row>
+    <row r="239" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B239" t="s">
+        <v>361</v>
+      </c>
+    </row>
+    <row r="240" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B240" t="s">
+        <v>272</v>
+      </c>
+    </row>
+    <row r="241" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B241" t="s">
+        <v>300</v>
+      </c>
+    </row>
+    <row r="242" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B242" s="2" t="s">
+        <v>370</v>
+      </c>
+    </row>
+  </sheetData>
+  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:B241">
+    <sortCondition ref="A2:A241"/>
+  </sortState>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00F92541-A7BF-DC45-86B3-5342D32CFEB3}">
+  <dimension ref="A1:C6"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
+  <cols>
+    <col min="1" max="1" width="14.33203125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="15" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="53.1640625" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" t="s">
+        <v>2</v>
+      </c>
+      <c r="C1" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="2" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A2" t="s">
+        <v>73</v>
+      </c>
+      <c r="B2">
+        <v>1</v>
+      </c>
+      <c r="C2" t="s">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A3" t="s">
+        <v>73</v>
+      </c>
+      <c r="B3">
+        <v>1</v>
+      </c>
+      <c r="C3" t="s">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="4" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A4" t="s">
+        <v>74</v>
+      </c>
+      <c r="B4">
+        <v>2</v>
+      </c>
+      <c r="C4" t="s">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="5" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A5" t="s">
+        <v>74</v>
+      </c>
+      <c r="B5">
+        <v>2</v>
+      </c>
+      <c r="C5" t="s">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="6" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A6" t="s">
+        <v>80</v>
+      </c>
+      <c r="B6">
+        <v>3</v>
+      </c>
+      <c r="C6" t="s">
+        <v>75</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{37E2A371-4B6C-DF4B-BB94-676313874EB3}">
+  <dimension ref="A1:B27"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
+  <cols>
+    <col min="1" max="1" width="34" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="29.5" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A1" t="s">
+        <v>505</v>
+      </c>
+      <c r="B1" t="s">
+        <v>480</v>
+      </c>
+    </row>
+    <row r="2" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A2" t="s">
+        <v>506</v>
+      </c>
+      <c r="B2" t="s">
+        <v>481</v>
+      </c>
+    </row>
+    <row r="3" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A3" t="s">
+        <v>507</v>
+      </c>
+      <c r="B3" t="s">
+        <v>482</v>
+      </c>
+    </row>
+    <row r="4" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A4" t="s">
+        <v>508</v>
+      </c>
+      <c r="B4" t="s">
+        <v>483</v>
+      </c>
+    </row>
+    <row r="5" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A5" t="s">
+        <v>509</v>
+      </c>
+      <c r="B5" t="s">
+        <v>484</v>
+      </c>
+    </row>
+    <row r="6" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A6" t="s">
+        <v>510</v>
+      </c>
+      <c r="B6" t="s">
+        <v>485</v>
+      </c>
+    </row>
+    <row r="7" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A7" t="s">
+        <v>511</v>
+      </c>
+      <c r="B7" t="s">
+        <v>486</v>
+      </c>
+    </row>
+    <row r="8" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A8" t="s">
+        <v>512</v>
+      </c>
+      <c r="B8" t="s">
+        <v>487</v>
+      </c>
+    </row>
+    <row r="9" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A9" t="s">
+        <v>513</v>
+      </c>
+      <c r="B9" t="s">
+        <v>488</v>
+      </c>
+    </row>
+    <row r="10" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A10" t="s">
+        <v>514</v>
+      </c>
+      <c r="B10" t="s">
+        <v>489</v>
+      </c>
+    </row>
+    <row r="11" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A11" t="s">
+        <v>515</v>
+      </c>
+      <c r="B11" t="s">
+        <v>490</v>
+      </c>
+    </row>
+    <row r="12" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A12" t="s">
+        <v>516</v>
+      </c>
+      <c r="B12" t="s">
+        <v>491</v>
+      </c>
+    </row>
+    <row r="13" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A13" t="s">
+        <v>517</v>
+      </c>
+      <c r="B13" t="s">
+        <v>492</v>
+      </c>
+    </row>
+    <row r="14" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A14" t="s">
+        <v>518</v>
+      </c>
+      <c r="B14" t="s">
+        <v>493</v>
+      </c>
+    </row>
+    <row r="15" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A15" t="s">
+        <v>519</v>
+      </c>
+      <c r="B15" t="s">
+        <v>494</v>
+      </c>
+    </row>
+    <row r="16" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A16" t="s">
+        <v>520</v>
+      </c>
+      <c r="B16" t="s">
+        <v>495</v>
+      </c>
+    </row>
+    <row r="17" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A17" t="s">
+        <v>521</v>
+      </c>
+      <c r="B17" t="s">
+        <v>496</v>
+      </c>
+    </row>
+    <row r="18" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A18" t="s">
+        <v>522</v>
+      </c>
+      <c r="B18" t="s">
+        <v>497</v>
+      </c>
+    </row>
+    <row r="19" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A19" t="s">
+        <v>523</v>
+      </c>
+      <c r="B19" t="s">
+        <v>498</v>
+      </c>
+    </row>
+    <row r="20" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A20" t="s">
+        <v>524</v>
+      </c>
+      <c r="B20" t="s">
+        <v>499</v>
+      </c>
+    </row>
+    <row r="21" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A21" t="s">
+        <v>525</v>
+      </c>
+      <c r="B21" t="s">
+        <v>500</v>
+      </c>
+    </row>
+    <row r="22" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A22" t="s">
+        <v>526</v>
+      </c>
+      <c r="B22" t="s">
+        <v>501</v>
+      </c>
+    </row>
+    <row r="23" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A23" t="s">
+        <v>527</v>
+      </c>
+      <c r="B23" t="s">
+        <v>502</v>
+      </c>
+    </row>
+    <row r="24" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A24" t="s">
+        <v>528</v>
+      </c>
+      <c r="B24" t="s">
+        <v>503</v>
+      </c>
+    </row>
+    <row r="25" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A25" t="s">
+        <v>529</v>
+      </c>
+      <c r="B25" t="s">
+        <v>504</v>
+      </c>
+    </row>
+    <row r="26" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A26" t="s">
+        <v>530</v>
+      </c>
+    </row>
+    <row r="27" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A27" t="s">
+        <v>531</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D5EFD653-B9DC-7049-B563-84BF8E10600B}">
   <dimension ref="A1:C24"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
@@ -1033,7 +4118,313 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2E7486C4-EC44-7041-9A77-2C6368EE7D6B}">
+  <dimension ref="A1:C13"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
+  <cols>
+    <col min="1" max="1" width="14.83203125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="15" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="24.33203125" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" t="s">
+        <v>2</v>
+      </c>
+      <c r="C1" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="2" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A2" t="s">
+        <v>119</v>
+      </c>
+      <c r="B2">
+        <v>1</v>
+      </c>
+      <c r="C2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A3" t="s">
+        <v>120</v>
+      </c>
+      <c r="B3">
+        <v>2</v>
+      </c>
+      <c r="C3">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="4" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A4" t="s">
+        <v>121</v>
+      </c>
+      <c r="B4">
+        <v>3</v>
+      </c>
+      <c r="C4">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="5" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A5" t="s">
+        <v>122</v>
+      </c>
+      <c r="B5">
+        <v>4</v>
+      </c>
+      <c r="C5">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="6" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A6" t="s">
+        <v>123</v>
+      </c>
+      <c r="B6">
+        <v>5</v>
+      </c>
+      <c r="C6">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="7" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A7" t="s">
+        <v>124</v>
+      </c>
+      <c r="B7">
+        <v>6</v>
+      </c>
+      <c r="C7">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="8" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A8" t="s">
+        <v>125</v>
+      </c>
+      <c r="B8">
+        <v>7</v>
+      </c>
+      <c r="C8">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="9" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A9" t="s">
+        <v>126</v>
+      </c>
+      <c r="B9">
+        <v>8</v>
+      </c>
+      <c r="C9">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="10" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A10" t="s">
+        <v>127</v>
+      </c>
+      <c r="B10">
+        <v>9</v>
+      </c>
+      <c r="C10">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="11" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A11" t="s">
+        <v>127</v>
+      </c>
+      <c r="B11">
+        <v>9</v>
+      </c>
+      <c r="C11">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="12" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A12" s="1" t="s">
+        <v>128</v>
+      </c>
+      <c r="B12" s="1" t="s">
+        <v>128</v>
+      </c>
+      <c r="C12" s="1" t="s">
+        <v>128</v>
+      </c>
+    </row>
+    <row r="13" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A13" t="s">
+        <v>127</v>
+      </c>
+      <c r="B13">
+        <v>9</v>
+      </c>
+      <c r="C13">
+        <v>99</v>
+      </c>
+    </row>
+  </sheetData>
+  <phoneticPr fontId="1" type="noConversion"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8C810785-5CED-B848-A707-E28390AD7500}">
+  <dimension ref="A1:C12"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
+  <cols>
+    <col min="1" max="1" width="17.6640625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="15" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="24.33203125" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" t="s">
+        <v>2</v>
+      </c>
+      <c r="C1" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="2" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A2" t="s">
+        <v>129</v>
+      </c>
+      <c r="B2">
+        <v>1</v>
+      </c>
+      <c r="C2" t="s">
+        <v>140</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A3" t="s">
+        <v>129</v>
+      </c>
+      <c r="B3">
+        <v>1</v>
+      </c>
+      <c r="C3" t="s">
+        <v>139</v>
+      </c>
+    </row>
+    <row r="4" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A4" t="s">
+        <v>130</v>
+      </c>
+      <c r="B4">
+        <v>2</v>
+      </c>
+      <c r="C4" t="s">
+        <v>130</v>
+      </c>
+    </row>
+    <row r="5" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A5" t="s">
+        <v>131</v>
+      </c>
+      <c r="B5">
+        <v>3</v>
+      </c>
+      <c r="C5" t="s">
+        <v>131</v>
+      </c>
+    </row>
+    <row r="6" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A6" t="s">
+        <v>132</v>
+      </c>
+      <c r="B6">
+        <v>4</v>
+      </c>
+      <c r="C6" t="s">
+        <v>132</v>
+      </c>
+    </row>
+    <row r="7" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A7" t="s">
+        <v>133</v>
+      </c>
+      <c r="B7">
+        <v>5</v>
+      </c>
+      <c r="C7" t="s">
+        <v>133</v>
+      </c>
+    </row>
+    <row r="8" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A8" t="s">
+        <v>134</v>
+      </c>
+      <c r="B8">
+        <v>6</v>
+      </c>
+      <c r="C8" t="s">
+        <v>134</v>
+      </c>
+    </row>
+    <row r="9" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A9" t="s">
+        <v>135</v>
+      </c>
+      <c r="B9">
+        <v>7</v>
+      </c>
+      <c r="C9" t="s">
+        <v>135</v>
+      </c>
+    </row>
+    <row r="10" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A10" t="s">
+        <v>136</v>
+      </c>
+      <c r="B10">
+        <v>8</v>
+      </c>
+      <c r="C10" t="s">
+        <v>136</v>
+      </c>
+    </row>
+    <row r="11" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A11" t="s">
+        <v>137</v>
+      </c>
+      <c r="B11">
+        <v>9</v>
+      </c>
+      <c r="C11" t="s">
+        <v>137</v>
+      </c>
+    </row>
+    <row r="12" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A12" t="s">
+        <v>138</v>
+      </c>
+      <c r="B12">
+        <v>10</v>
+      </c>
+      <c r="C12" t="s">
+        <v>138</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3843C77D-358A-B149-8D8B-2D0A3CF1F42F}">
   <dimension ref="A1:C27"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
@@ -1059,8 +4450,7 @@
         <v>16</v>
       </c>
       <c r="B2">
-        <f t="shared" ref="B2:B26" si="0">E2+1</f>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C2" t="s">
         <v>23</v>
@@ -1071,8 +4461,7 @@
         <v>16</v>
       </c>
       <c r="B3">
-        <f t="shared" si="0"/>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C3" t="s">
         <v>29</v>
@@ -1083,8 +4472,7 @@
         <v>16</v>
       </c>
       <c r="B4">
-        <f t="shared" si="0"/>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C4" t="s">
         <v>30</v>
@@ -1095,8 +4483,7 @@
         <v>16</v>
       </c>
       <c r="B5">
-        <f t="shared" si="0"/>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C5" t="s">
         <v>31</v>
@@ -1107,8 +4494,7 @@
         <v>16</v>
       </c>
       <c r="B6">
-        <f t="shared" si="0"/>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C6" t="s">
         <v>32</v>
@@ -1119,8 +4505,7 @@
         <v>16</v>
       </c>
       <c r="B7">
-        <f t="shared" si="0"/>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C7" t="s">
         <v>33</v>
@@ -1131,8 +4516,7 @@
         <v>16</v>
       </c>
       <c r="B8">
-        <f t="shared" si="0"/>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C8" t="s">
         <v>34</v>
@@ -1143,8 +4527,7 @@
         <v>16</v>
       </c>
       <c r="B9">
-        <f t="shared" si="0"/>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C9" t="s">
         <v>35</v>
@@ -1155,8 +4538,7 @@
         <v>16</v>
       </c>
       <c r="B10">
-        <f t="shared" si="0"/>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C10" t="s">
         <v>36</v>
@@ -1167,8 +4549,7 @@
         <v>16</v>
       </c>
       <c r="B11">
-        <f t="shared" si="0"/>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C11" t="s">
         <v>37</v>
@@ -1179,8 +4560,7 @@
         <v>16</v>
       </c>
       <c r="B12">
-        <f t="shared" si="0"/>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C12" t="s">
         <v>38</v>
@@ -1191,8 +4571,7 @@
         <v>16</v>
       </c>
       <c r="B13">
-        <f t="shared" si="0"/>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C13" t="s">
         <v>39</v>
@@ -1203,8 +4582,7 @@
         <v>24</v>
       </c>
       <c r="B14">
-        <f t="shared" si="0"/>
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="C14" t="s">
         <v>40</v>
@@ -1215,8 +4593,7 @@
         <v>25</v>
       </c>
       <c r="B15">
-        <f t="shared" si="0"/>
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="C15" t="s">
         <v>41</v>
@@ -1227,8 +4604,7 @@
         <v>26</v>
       </c>
       <c r="B16">
-        <f t="shared" si="0"/>
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="C16" t="s">
         <v>42</v>
@@ -1239,8 +4615,7 @@
         <v>17</v>
       </c>
       <c r="B17">
-        <f t="shared" si="0"/>
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="C17" t="s">
         <v>43</v>
@@ -1251,8 +4626,7 @@
         <v>18</v>
       </c>
       <c r="B18">
-        <f t="shared" si="0"/>
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="C18" t="s">
         <v>81</v>
@@ -1263,8 +4637,7 @@
         <v>18</v>
       </c>
       <c r="B19">
-        <f t="shared" si="0"/>
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="C19" t="s">
         <v>82</v>
@@ -1275,8 +4648,7 @@
         <v>19</v>
       </c>
       <c r="B20">
-        <f t="shared" si="0"/>
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="C20" t="s">
         <v>83</v>
@@ -1287,8 +4659,7 @@
         <v>19</v>
       </c>
       <c r="B21">
-        <f t="shared" si="0"/>
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="C21" t="s">
         <v>84</v>
@@ -1299,8 +4670,7 @@
         <v>20</v>
       </c>
       <c r="B22">
-        <f t="shared" si="0"/>
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="C22" t="s">
         <v>85</v>
@@ -1311,8 +4681,7 @@
         <v>21</v>
       </c>
       <c r="B23">
-        <f t="shared" si="0"/>
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="C23" t="s">
         <v>86</v>
@@ -1323,8 +4692,7 @@
         <v>22</v>
       </c>
       <c r="B24">
-        <f t="shared" si="0"/>
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="C24" t="s">
         <v>87</v>
@@ -1335,8 +4703,7 @@
         <v>22</v>
       </c>
       <c r="B25">
-        <f t="shared" si="0"/>
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="C25" t="s">
         <v>88</v>
@@ -1347,8 +4714,7 @@
         <v>22</v>
       </c>
       <c r="B26">
-        <f t="shared" si="0"/>
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="C26" t="s">
         <v>89</v>
@@ -1371,7 +4737,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D4258749-6AA6-894F-B100-962D7468D8C9}">
   <dimension ref="A1:C5"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
@@ -1441,7 +4807,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3E352EA4-A105-114E-B204-10F001C5F062}">
   <dimension ref="A1:C18"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
@@ -1654,7 +5020,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3A123FFA-1FB5-5F4B-8695-D5DF4C6EF596}">
   <dimension ref="A1:C10"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
@@ -1777,83 +5143,274 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00F92541-A7BF-DC45-86B3-5342D32CFEB3}">
-  <dimension ref="A1:C6"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
-  <cols>
-    <col min="1" max="1" width="14.33203125" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="15" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="53.1640625" bestFit="1" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" t="s">
-        <v>2</v>
-      </c>
-      <c r="C1" t="s">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A2" t="s">
-        <v>73</v>
-      </c>
-      <c r="B2">
-        <v>1</v>
-      </c>
-      <c r="C2" t="s">
-        <v>76</v>
-      </c>
-    </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A3" t="s">
-        <v>73</v>
-      </c>
-      <c r="B3">
-        <v>1</v>
-      </c>
-      <c r="C3" t="s">
-        <v>77</v>
-      </c>
-    </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A4" t="s">
-        <v>74</v>
-      </c>
-      <c r="B4">
-        <v>2</v>
-      </c>
-      <c r="C4" t="s">
-        <v>78</v>
-      </c>
-    </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A5" t="s">
-        <v>74</v>
-      </c>
-      <c r="B5">
-        <v>2</v>
-      </c>
-      <c r="C5" t="s">
-        <v>79</v>
-      </c>
-    </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A6" t="s">
-        <v>80</v>
-      </c>
-      <c r="B6">
-        <v>3</v>
-      </c>
-      <c r="C6" t="s">
-        <v>75</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
+<file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x0101001F94058304E35D4BA41C971EED53A900" ma:contentTypeVersion="13" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="b1d50a519dadc8ad715d0e90461ded02">
+  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="d0698e67-e062-4b57-883b-8b4e092c8e9a" xmlns:ns3="67e7f70a-be5a-465c-90b1-ee657733946e" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="47a0d717dc720d3e89a1e53d093506cc" ns2:_="" ns3:_="">
+    <xsd:import namespace="d0698e67-e062-4b57-883b-8b4e092c8e9a"/>
+    <xsd:import namespace="67e7f70a-be5a-465c-90b1-ee657733946e"/>
+    <xsd:element name="properties">
+      <xsd:complexType>
+        <xsd:sequence>
+          <xsd:element name="documentManagement">
+            <xsd:complexType>
+              <xsd:all>
+                <xsd:element ref="ns2:MediaServiceMetadata" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceFastMetadata" minOccurs="0"/>
+                <xsd:element ref="ns3:SharedWithUsers" minOccurs="0"/>
+                <xsd:element ref="ns3:SharedWithDetails" minOccurs="0"/>
+                <xsd:element ref="ns2:lcf76f155ced4ddcb4097134ff3c332f" minOccurs="0"/>
+                <xsd:element ref="ns3:TaxCatchAll" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceObjectDetectorVersions" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceOCR" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceGenerationTime" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceEventHashCode" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceDateTaken" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceSearchProperties" minOccurs="0"/>
+              </xsd:all>
+            </xsd:complexType>
+          </xsd:element>
+        </xsd:sequence>
+      </xsd:complexType>
+    </xsd:element>
+  </xsd:schema>
+  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:dms="http://schemas.microsoft.com/office/2006/documentManagement/types" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" targetNamespace="d0698e67-e062-4b57-883b-8b4e092c8e9a" elementFormDefault="qualified">
+    <xsd:import namespace="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <xsd:import namespace="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <xsd:element name="MediaServiceMetadata" ma:index="8" nillable="true" ma:displayName="MediaServiceMetadata" ma:hidden="true" ma:internalName="MediaServiceMetadata" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Note"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceFastMetadata" ma:index="9" nillable="true" ma:displayName="MediaServiceFastMetadata" ma:hidden="true" ma:internalName="MediaServiceFastMetadata" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Note"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="lcf76f155ced4ddcb4097134ff3c332f" ma:index="13" nillable="true" ma:taxonomy="true" ma:internalName="lcf76f155ced4ddcb4097134ff3c332f" ma:taxonomyFieldName="MediaServiceImageTags" ma:displayName="Image Tags" ma:readOnly="false" ma:fieldId="{5cf76f15-5ced-4ddc-b409-7134ff3c332f}" ma:taxonomyMulti="true" ma:sspId="30fdde71-3d84-4f2a-8a39-a81d5da30a6e" ma:termSetId="09814cd3-568e-fe90-9814-8d621ff8fb84" ma:anchorId="fba54fb3-c3e1-fe81-a776-ca4b69148c4d" ma:open="true" ma:isKeyword="false">
+      <xsd:complexType>
+        <xsd:sequence>
+          <xsd:element ref="pc:Terms" minOccurs="0" maxOccurs="1"/>
+        </xsd:sequence>
+      </xsd:complexType>
+    </xsd:element>
+    <xsd:element name="MediaServiceObjectDetectorVersions" ma:index="15" nillable="true" ma:displayName="MediaServiceObjectDetectorVersions" ma:hidden="true" ma:indexed="true" ma:internalName="MediaServiceObjectDetectorVersions" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Text"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceOCR" ma:index="16" nillable="true" ma:displayName="Extracted Text" ma:internalName="MediaServiceOCR" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Note">
+          <xsd:maxLength value="255"/>
+        </xsd:restriction>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceGenerationTime" ma:index="17" nillable="true" ma:displayName="MediaServiceGenerationTime" ma:hidden="true" ma:internalName="MediaServiceGenerationTime" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Text"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceEventHashCode" ma:index="18" nillable="true" ma:displayName="MediaServiceEventHashCode" ma:hidden="true" ma:internalName="MediaServiceEventHashCode" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Text"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceDateTaken" ma:index="19" nillable="true" ma:displayName="MediaServiceDateTaken" ma:hidden="true" ma:indexed="true" ma:internalName="MediaServiceDateTaken" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Text"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceSearchProperties" ma:index="20" nillable="true" ma:displayName="MediaServiceSearchProperties" ma:hidden="true" ma:internalName="MediaServiceSearchProperties" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Note"/>
+      </xsd:simpleType>
+    </xsd:element>
+  </xsd:schema>
+  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:dms="http://schemas.microsoft.com/office/2006/documentManagement/types" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" targetNamespace="67e7f70a-be5a-465c-90b1-ee657733946e" elementFormDefault="qualified">
+    <xsd:import namespace="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <xsd:import namespace="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <xsd:element name="SharedWithUsers" ma:index="10" nillable="true" ma:displayName="Shared With" ma:internalName="SharedWithUsers" ma:readOnly="true">
+      <xsd:complexType>
+        <xsd:complexContent>
+          <xsd:extension base="dms:UserMulti">
+            <xsd:sequence>
+              <xsd:element name="UserInfo" minOccurs="0" maxOccurs="unbounded">
+                <xsd:complexType>
+                  <xsd:sequence>
+                    <xsd:element name="DisplayName" type="xsd:string" minOccurs="0"/>
+                    <xsd:element name="AccountId" type="dms:UserId" minOccurs="0" nillable="true"/>
+                    <xsd:element name="AccountType" type="xsd:string" minOccurs="0"/>
+                  </xsd:sequence>
+                </xsd:complexType>
+              </xsd:element>
+            </xsd:sequence>
+          </xsd:extension>
+        </xsd:complexContent>
+      </xsd:complexType>
+    </xsd:element>
+    <xsd:element name="SharedWithDetails" ma:index="11" nillable="true" ma:displayName="Shared With Details" ma:internalName="SharedWithDetails" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Note">
+          <xsd:maxLength value="255"/>
+        </xsd:restriction>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="TaxCatchAll" ma:index="14" nillable="true" ma:displayName="Taxonomy Catch All Column" ma:hidden="true" ma:list="{fba810b6-f49d-43b4-8b30-720f39d3e2f5}" ma:internalName="TaxCatchAll" ma:showField="CatchAllData" ma:web="67e7f70a-be5a-465c-90b1-ee657733946e">
+      <xsd:complexType>
+        <xsd:complexContent>
+          <xsd:extension base="dms:MultiChoiceLookup">
+            <xsd:sequence>
+              <xsd:element name="Value" type="dms:Lookup" maxOccurs="unbounded" minOccurs="0" nillable="true"/>
+            </xsd:sequence>
+          </xsd:extension>
+        </xsd:complexContent>
+      </xsd:complexType>
+    </xsd:element>
+  </xsd:schema>
+  <xsd:schema xmlns="http://schemas.openxmlformats.org/package/2006/metadata/core-properties" xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:dc="http://purl.org/dc/elements/1.1/" xmlns:dcterms="http://purl.org/dc/terms/" xmlns:odoc="http://schemas.microsoft.com/internal/obd" targetNamespace="http://schemas.openxmlformats.org/package/2006/metadata/core-properties" elementFormDefault="qualified" attributeFormDefault="unqualified" blockDefault="#all">
+    <xsd:import namespace="http://purl.org/dc/elements/1.1/" schemaLocation="http://dublincore.org/schemas/xmls/qdc/2003/04/02/dc.xsd"/>
+    <xsd:import namespace="http://purl.org/dc/terms/" schemaLocation="http://dublincore.org/schemas/xmls/qdc/2003/04/02/dcterms.xsd"/>
+    <xsd:element name="coreProperties" type="CT_coreProperties"/>
+    <xsd:complexType name="CT_coreProperties">
+      <xsd:all>
+        <xsd:element ref="dc:creator" minOccurs="0" maxOccurs="1"/>
+        <xsd:element ref="dcterms:created" minOccurs="0" maxOccurs="1"/>
+        <xsd:element ref="dc:identifier" minOccurs="0" maxOccurs="1"/>
+        <xsd:element name="contentType" minOccurs="0" maxOccurs="1" type="xsd:string" ma:index="0" ma:displayName="Content Type"/>
+        <xsd:element ref="dc:title" minOccurs="0" maxOccurs="1" ma:index="4" ma:displayName="Title"/>
+        <xsd:element ref="dc:subject" minOccurs="0" maxOccurs="1"/>
+        <xsd:element ref="dc:description" minOccurs="0" maxOccurs="1"/>
+        <xsd:element name="keywords" minOccurs="0" maxOccurs="1" type="xsd:string"/>
+        <xsd:element ref="dc:language" minOccurs="0" maxOccurs="1"/>
+        <xsd:element name="category" minOccurs="0" maxOccurs="1" type="xsd:string"/>
+        <xsd:element name="version" minOccurs="0" maxOccurs="1" type="xsd:string"/>
+        <xsd:element name="revision" minOccurs="0" maxOccurs="1" type="xsd:string">
+          <xsd:annotation>
+            <xsd:documentation>
+                        This value indicates the number of saves or revisions. The application is responsible for updating this value after each revision.
+                    </xsd:documentation>
+          </xsd:annotation>
+        </xsd:element>
+        <xsd:element name="lastModifiedBy" minOccurs="0" maxOccurs="1" type="xsd:string"/>
+        <xsd:element ref="dcterms:modified" minOccurs="0" maxOccurs="1"/>
+        <xsd:element name="contentStatus" minOccurs="0" maxOccurs="1" type="xsd:string"/>
+      </xsd:all>
+    </xsd:complexType>
+  </xsd:schema>
+  <xs:schema xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" xmlns:xs="http://www.w3.org/2001/XMLSchema" targetNamespace="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" elementFormDefault="qualified" attributeFormDefault="unqualified">
+    <xs:element name="Person">
+      <xs:complexType>
+        <xs:sequence>
+          <xs:element ref="pc:DisplayName" minOccurs="0"/>
+          <xs:element ref="pc:AccountId" minOccurs="0"/>
+          <xs:element ref="pc:AccountType" minOccurs="0"/>
+        </xs:sequence>
+      </xs:complexType>
+    </xs:element>
+    <xs:element name="DisplayName" type="xs:string"/>
+    <xs:element name="AccountId" type="xs:string"/>
+    <xs:element name="AccountType" type="xs:string"/>
+    <xs:element name="BDCAssociatedEntity">
+      <xs:complexType>
+        <xs:sequence>
+          <xs:element ref="pc:BDCEntity" minOccurs="0" maxOccurs="unbounded"/>
+        </xs:sequence>
+        <xs:attribute ref="pc:EntityNamespace"/>
+        <xs:attribute ref="pc:EntityName"/>
+        <xs:attribute ref="pc:SystemInstanceName"/>
+        <xs:attribute ref="pc:AssociationName"/>
+      </xs:complexType>
+    </xs:element>
+    <xs:attribute name="EntityNamespace" type="xs:string"/>
+    <xs:attribute name="EntityName" type="xs:string"/>
+    <xs:attribute name="SystemInstanceName" type="xs:string"/>
+    <xs:attribute name="AssociationName" type="xs:string"/>
+    <xs:element name="BDCEntity">
+      <xs:complexType>
+        <xs:sequence>
+          <xs:element ref="pc:EntityDisplayName" minOccurs="0"/>
+          <xs:element ref="pc:EntityInstanceReference" minOccurs="0"/>
+          <xs:element ref="pc:EntityId1" minOccurs="0"/>
+          <xs:element ref="pc:EntityId2" minOccurs="0"/>
+          <xs:element ref="pc:EntityId3" minOccurs="0"/>
+          <xs:element ref="pc:EntityId4" minOccurs="0"/>
+          <xs:element ref="pc:EntityId5" minOccurs="0"/>
+        </xs:sequence>
+      </xs:complexType>
+    </xs:element>
+    <xs:element name="EntityDisplayName" type="xs:string"/>
+    <xs:element name="EntityInstanceReference" type="xs:string"/>
+    <xs:element name="EntityId1" type="xs:string"/>
+    <xs:element name="EntityId2" type="xs:string"/>
+    <xs:element name="EntityId3" type="xs:string"/>
+    <xs:element name="EntityId4" type="xs:string"/>
+    <xs:element name="EntityId5" type="xs:string"/>
+    <xs:element name="Terms">
+      <xs:complexType>
+        <xs:sequence>
+          <xs:element ref="pc:TermInfo" minOccurs="0" maxOccurs="unbounded"/>
+        </xs:sequence>
+      </xs:complexType>
+    </xs:element>
+    <xs:element name="TermInfo">
+      <xs:complexType>
+        <xs:sequence>
+          <xs:element ref="pc:TermName" minOccurs="0"/>
+          <xs:element ref="pc:TermId" minOccurs="0"/>
+        </xs:sequence>
+      </xs:complexType>
+    </xs:element>
+    <xs:element name="TermName" type="xs:string"/>
+    <xs:element name="TermId" type="xs:string"/>
+  </xs:schema>
+</ct:contentTypeSchema>
+</file>
+
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <TaxCatchAll xmlns="67e7f70a-be5a-465c-90b1-ee657733946e" xsi:nil="true"/>
+    <lcf76f155ced4ddcb4097134ff3c332f xmlns="d0698e67-e062-4b57-883b-8b4e092c8e9a">
+      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    </lcf76f155ced4ddcb4097134ff3c332f>
+  </documentManagement>
+</p:properties>
+</file>
+
+<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{DEEF4CD1-2DB2-4758-BD3B-413FF7573B38}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{A7120EC9-9C3F-48D2-9F54-D3DBB9D6E67D}"/>
+</file>
+
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{47D6C30E-F42C-4149-AFA1-F6EE4E6E3324}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="d0698e67-e062-4b57-883b-8b4e092c8e9a"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/dcmitype/"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
+    <ds:schemaRef ds:uri="http://www.w3.org/XML/1998/namespace"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
+    <ds:schemaRef ds:uri="67e7f70a-be5a-465c-90b1-ee657733946e"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>